--- a/data/trans_bre/P16A15-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A15-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 5,07</t>
+          <t>-0,36; 5,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 5,5</t>
+          <t>-1,76; 5,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 5,52</t>
+          <t>-1,36; 5,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 5,03</t>
+          <t>-1,34; 4,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 107,42</t>
+          <t>-6,2; 109,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 51,56</t>
+          <t>-12,7; 53,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 53,91</t>
+          <t>-10,28; 54,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 43,78</t>
+          <t>-9,02; 38,39</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,94</t>
+          <t>0,8; 5,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,29</t>
+          <t>-1,18; 4,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 5,62</t>
+          <t>-0,38; 5,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 9,51</t>
+          <t>1,28; 10,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,95; 123,27</t>
+          <t>8,86; 114,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 49,29</t>
+          <t>-10,28; 55,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 69,62</t>
+          <t>-3,75; 60,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,33; 201,27</t>
+          <t>10,82; 179,87</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,44</t>
+          <t>-0,61; 4,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 6,79</t>
+          <t>-0,02; 6,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 1,39</t>
+          <t>-4,6; 1,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 51,53</t>
+          <t>-1,93; 56,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 101,83</t>
+          <t>-9,81; 110,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 91,9</t>
+          <t>0,65; 86,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,31; 19,89</t>
+          <t>-42,65; 17,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 467,14</t>
+          <t>-15,36; 526,38</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,97</t>
+          <t>-1,12; 3,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 4,26</t>
+          <t>-1,73; 4,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 5,8</t>
+          <t>0,38; 5,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 4,69</t>
+          <t>-1,4; 4,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,16; 59,75</t>
+          <t>-17,02; 59,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 46,91</t>
+          <t>-15,24; 48,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,95; 95,41</t>
+          <t>3,96; 91,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 41,78</t>
+          <t>-10,1; 42,99</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,38</t>
+          <t>0,83; 3,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,63</t>
+          <t>0,36; 3,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,14</t>
+          <t>0,16; 3,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 23,36</t>
+          <t>1,59; 22,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,64; 63,22</t>
+          <t>13,13; 61,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,49; 37,98</t>
+          <t>3,86; 38,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 35,28</t>
+          <t>1,35; 34,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,59; 222,99</t>
+          <t>13,57; 227,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A15-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A15-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,79</t>
+          <t>1,72</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 5,12</t>
+          <t>-0,12; 5,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 5,41</t>
+          <t>-1,86; 5,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 5,51</t>
+          <t>-1,5; 5,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 4,82</t>
+          <t>-1,38; 4,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 109,49</t>
+          <t>-1,9; 110,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 53,77</t>
+          <t>-14,0; 53,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 54,09</t>
+          <t>-11,94; 54,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 38,39</t>
+          <t>-9,13; 41,33</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,61</t>
+          <t>2,29</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,74</t>
+          <t>1,04; 5,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,7</t>
+          <t>-1,13; 4,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,17</t>
+          <t>-0,58; 5,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 10,0</t>
+          <t>-0,3; 4,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,86; 114,49</t>
+          <t>12,16; 120,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 55,43</t>
+          <t>-10,83; 50,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 60,87</t>
+          <t>-5,09; 63,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,82; 179,87</t>
+          <t>-3,07; 45,87</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,58</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>152,21%</t>
+          <t>-4,01%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 4,52</t>
+          <t>-0,63; 4,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 6,5</t>
+          <t>0,52; 7,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 1,46</t>
+          <t>-4,64; 0,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 56,44</t>
+          <t>-3,23; 2,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 110,65</t>
+          <t>-9,72; 102,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 86,87</t>
+          <t>3,08; 99,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-42,65; 17,43</t>
+          <t>-42,25; 11,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 526,38</t>
+          <t>-23,56; 25,48</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,85</t>
+          <t>3,33</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,07</t>
+          <t>-1,2; 3,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 4,18</t>
+          <t>-1,5; 4,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 5,81</t>
+          <t>0,52; 6,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 4,78</t>
+          <t>0,78; 5,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 59,71</t>
+          <t>-18,26; 64,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 48,22</t>
+          <t>-12,79; 54,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 91,36</t>
+          <t>7,33; 98,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 42,99</t>
+          <t>5,66; 54,26</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>1,9</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,24</t>
+          <t>0,86; 3,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,68</t>
+          <t>0,44; 3,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,1</t>
+          <t>0,1; 3,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 22,44</t>
+          <t>0,58; 3,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,13; 61,62</t>
+          <t>13,46; 62,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,86; 38,66</t>
+          <t>3,95; 36,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 34,84</t>
+          <t>0,76; 35,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,57; 227,26</t>
+          <t>4,5; 28,87</t>
         </is>
       </c>
     </row>
